--- a/User_Data/Watchlists/aus_pop/aus_pop.xlsx
+++ b/User_Data/Watchlists/aus_pop/aus_pop.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,6 +1084,138 @@
         </is>
       </c>
       <c r="D30" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>A2325981V</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A2325981V</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Index Numbers ;  Housing ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>A2325946L</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A2325946L</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Index Numbers ;  Housing ;  Melbourne ;</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Male ;  New South Wales ;</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Female ;  New South Wales ;</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Female ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Persons ;  New South Wales ;</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>abs_series</t>
         </is>
@@ -1100,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1249,6 +1381,36 @@
           <t>A2326391L</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>A2325946L</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>A2325981V</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1397,6 +1559,36 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -1437,6 +1629,12 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1473,6 +1671,12 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1621,6 +1825,36 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -1661,6 +1895,12 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1697,6 +1937,12 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1845,6 +2091,36 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>abs_series</t>
         </is>
@@ -1885,6 +2161,12 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1921,6 +2203,12 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1957,6 +2245,12 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1993,6 +2287,12 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2029,6 +2329,12 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2065,6 +2371,12 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2101,6 +2413,12 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2137,6 +2455,12 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2289,6 +2613,36 @@
           <t>A2326391L</t>
         </is>
       </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>A2325946L</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>A2325981V</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2439,6 +2793,36 @@
       <c r="AD18" t="inlineStr">
         <is>
           <t>A2326391L</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>A2325946L</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>A2325981V</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
         </is>
       </c>
     </row>
@@ -2477,6 +2861,12 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/User_Data/Watchlists/aus_pop/aus_pop.xlsx
+++ b/User_Data/Watchlists/aus_pop/aus_pop.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,6 +1040,50 @@
         </is>
       </c>
       <c r="D28" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>A2325941A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A2325941A</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Index Numbers ;  Housing ;  Sydney ;</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>A2326391L</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A2326391L</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Index Numbers ;  Rents ;  Sydney ;1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>abs_series</t>
         </is>
@@ -1056,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1239,16 @@
           <t>A85232568L,340101</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>A2325941A</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>A2326391L</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1333,6 +1387,16 @@
         </is>
       </c>
       <c r="AB2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -1371,6 +1435,8 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1405,6 +1471,8 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1543,6 +1611,16 @@
         </is>
       </c>
       <c r="AB5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -1581,6 +1659,8 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1615,6 +1695,8 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1753,6 +1835,16 @@
         </is>
       </c>
       <c r="AB8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>abs_series</t>
         </is>
@@ -1791,6 +1883,8 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1825,6 +1919,8 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1859,6 +1955,8 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1893,6 +1991,8 @@
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1927,6 +2027,8 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1961,6 +2063,8 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1995,6 +2099,8 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2029,6 +2135,8 @@
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2171,6 +2279,16 @@
           <t>A85232568L,340101</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>A2325941A</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>A2326391L</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2311,6 +2429,16 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>A85232568L,340101</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>A2325941A</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>A2326391L</t>
         </is>
       </c>
     </row>
@@ -2347,6 +2475,8 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/User_Data/Watchlists/aus_pop/aus_pop.xlsx
+++ b/User_Data/Watchlists/aus_pop/aus_pop.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="watchlist" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="all_metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="full_metadata" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,17 +18,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +47,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,33 +419,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>GLFSEPTPOP</t>
         </is>
@@ -464,7 +457,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Employment to population ratio</t>
+          <t>Error_GLFSEPTPOP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +467,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>australia/population</t>
         </is>
@@ -496,7 +489,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A2133244X</t>
         </is>
@@ -508,7 +501,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Births ;  Australia ;</t>
+          <t>A2133244X</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -518,7 +511,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>A2133245A</t>
         </is>
@@ -530,7 +523,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deaths ;  Australia ;</t>
+          <t>A2133245A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -540,7 +533,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A2133252X</t>
         </is>
@@ -552,7 +545,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natural Increase ;  Australia ;</t>
+          <t>A2133252X</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -562,7 +555,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A2133246C</t>
         </is>
@@ -574,7 +567,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Interstate Arrivals ;  Australia ;</t>
+          <t>A2133246C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -584,7 +577,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A2133247F</t>
         </is>
@@ -596,7 +589,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Interstate Departures ;  Australia ;</t>
+          <t>A2133247F</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -606,7 +599,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A2133248J</t>
         </is>
@@ -618,7 +611,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Overseas Arrivals ;  Australia ;</t>
+          <t>A2133248J</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -628,7 +621,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A2133249K</t>
         </is>
@@ -640,7 +633,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Overseas Departures ;  Australia ;</t>
+          <t>A2133249K</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -650,7 +643,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A2133253A</t>
         </is>
@@ -662,7 +655,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Net Permanent and Long Term Movement ;  Australia ;</t>
+          <t>A2133253A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -672,7 +665,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A2133250V</t>
         </is>
@@ -684,7 +677,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Migration Adjustment ;  Australia ;</t>
+          <t>A2133250V</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -694,7 +687,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A2133254C</t>
         </is>
@@ -706,7 +699,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Net Overseas Migration ;  Australia ;</t>
+          <t>A2133254C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -716,7 +709,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A2133251W</t>
         </is>
@@ -728,7 +721,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estimated Resident Population (ERP) ;  Australia ;</t>
+          <t>A2133251W</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -738,7 +731,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A2133255F</t>
         </is>
@@ -750,7 +743,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ERP Change Over Previous Year ;  Australia ;</t>
+          <t>A2133255F</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -760,7 +753,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A2133256J</t>
         </is>
@@ -772,7 +765,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Percentage ERP Change Over Previous Year ;  Australia ;</t>
+          <t>A2133256J</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -782,7 +775,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A85232567K</t>
         </is>
@@ -794,7 +787,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Number of movements ;  Permanent Arrivals ;</t>
+          <t>A85232567K</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -804,7 +797,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A85232568L</t>
         </is>
@@ -816,7 +809,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Number of movements ;  Permanent and Long-term Arrivals ;</t>
+          <t>A85232568L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -826,7 +819,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A85232561W</t>
         </is>
@@ -838,7 +831,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Number of movements ;  Total Arrivals ;</t>
+          <t>A85232561W</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -848,7 +841,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A2060784V</t>
         </is>
@@ -860,7 +853,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Natural Increase ;  Australia ;</t>
+          <t>A2060784V</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -870,7 +863,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A2060785W</t>
         </is>
@@ -882,7 +875,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net Overseas Migration ;  Australia ;</t>
+          <t>A2060785W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -892,7 +885,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A85232566J</t>
         </is>
@@ -904,7 +897,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Number of movements ;  Permanent Departures ;</t>
+          <t>A85232566J</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -914,7 +907,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A85232570X</t>
         </is>
@@ -926,7 +919,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Number of movements ;  Total Departures ;</t>
+          <t>A85232570X</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -936,7 +929,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A2603609J</t>
         </is>
@@ -948,7 +941,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Quarterly Index ;  Total hourly rates of pay excluding bonuses ;  Australia ;  Private and Public ;  All industries ;</t>
+          <t>A2603609J</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -958,7 +951,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A2603610T</t>
         </is>
@@ -970,7 +963,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Percentage Change from Previous Quarter ;  Total hourly rates of pay excluding bonuses ;  Australia ;  Private and Public ;  All industries ;</t>
+          <t>A2603610T</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -980,7 +973,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A2060842F</t>
         </is>
@@ -992,7 +985,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estimated Resident Population ;  Persons ;  Australia ;</t>
+          <t>A2060842F</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1002,7 +995,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A85232558J,340102</t>
         </is>
@@ -1014,7 +1007,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Number of movements ;  Permanent and Long-term Departures ;</t>
+          <t>Error_A85232558J,340102</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1024,7 +1017,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A85232568L,340101</t>
         </is>
@@ -1036,7 +1029,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Number of movements ;  Permanent and Long-term Arrivals ;</t>
+          <t>Error_A85232568L,340101</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1046,7 +1039,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A2325941A</t>
         </is>
@@ -1058,7 +1051,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Index Numbers ;  Housing ;  Sydney ;</t>
+          <t>Error_A2325941A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1068,7 +1061,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A2326391L</t>
         </is>
@@ -1080,7 +1073,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Index Numbers ;  Rents ;  Sydney ;1</t>
+          <t>Error_A2326391L</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1090,7 +1083,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A2325981V</t>
         </is>
@@ -1102,7 +1095,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Index Numbers ;  Housing ;  Australia ;</t>
+          <t>Error_A2325981V</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1112,7 +1105,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A2325946L</t>
         </is>
@@ -1124,7 +1117,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Index Numbers ;  Housing ;  Melbourne ;</t>
+          <t>Error_A2325946L</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1134,7 +1127,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A2060825C</t>
         </is>
@@ -1146,7 +1139,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estimated Resident Population ;  Male ;  New South Wales ;</t>
+          <t>A2060825C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1156,7 +1149,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A2060834F</t>
         </is>
@@ -1168,7 +1161,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estimated Resident Population ;  Female ;  New South Wales ;</t>
+          <t>A2060834F</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1178,7 +1171,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A2060833C</t>
         </is>
@@ -1190,7 +1183,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estimated Resident Population ;  Female ;  Australia ;</t>
+          <t>A2060833C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1200,7 +1193,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A2060843J</t>
         </is>
@@ -1212,10 +1205,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estimated Resident Population ;  Persons ;  New South Wales ;</t>
+          <t>A2060843J</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>abs_series</t>
         </is>
@@ -1232,188 +1247,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>GLFSEPTPOP</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>australia/population</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>A2133244X</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>A2133245A</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>A2133246C</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>A2133247F</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>A2133248J</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>A2133249K</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A2133251W</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>A2133255F</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>A2133256J</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>A85232567K</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>A85232568L</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>A85232561W</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>A85232566J</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>A85232570X</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>A2603609J</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>A2603610T</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>A2060842F</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>A2133252X</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>A2133253A</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>A2133250V</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>A2133254C</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>A2060784V</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>A2060785W</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>A85232558J,340102</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>A85232568L,340101</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>A2325941A</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>A2326391L</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>A2325946L</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>A2325981V</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>A2060825C</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>A2060834F</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>A2060833C</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>A2060843J</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>units</t>
         </is>
@@ -1425,261 +1445,492 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Million</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Index Numbers</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Persons</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Persons</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Persons</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Persons</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Persons</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Number</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>series_type</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>data_type</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PERCENT</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>INDEX</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>PERCENT</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -1691,225 +1942,351 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>YS-JAN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Month</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>frequency_short</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>YS-JAN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>original_source</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Australian Bureau of Statistics</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -1943,9 +2320,10 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -2125,15 +2503,24 @@
           <t>abs_series</t>
         </is>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>abs_series</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The population of Australia represents 0.33 percent of the world´s total population which arguably means that one person in every 308 people on the planet is a resident of Australia.</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -2167,93 +2554,212 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+      <c r="C10" s="1" t="n">
+        <v>42370</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>27760</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>27760</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>27760</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>27760</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>27760</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>35674</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>35674</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>29738</v>
+      </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AG10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>29738</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>27760</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="C11" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>45809</v>
+      </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AG11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="AH11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>45931</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -2293,135 +2799,313 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>min_value</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="D13" t="n">
+        <v>55</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>14923.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>410</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1870</v>
+      </c>
+      <c r="O13" t="n">
+        <v>14940</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>30330</v>
+      </c>
+      <c r="R13" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>14923260</v>
+      </c>
+      <c r="U13" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-27.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-42.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>22875</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-42551</v>
+      </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AG13" t="n">
+        <v>2608351</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2626538</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7474993</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>5234889</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>3150</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>max_value</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="D14" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>27614.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>661.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M14" t="n">
+        <v>16400</v>
+      </c>
+      <c r="N14" t="n">
+        <v>159610</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2383330</v>
+      </c>
+      <c r="P14" t="n">
+        <v>9720</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2262020</v>
+      </c>
+      <c r="R14" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>27614411</v>
+      </c>
+      <c r="U14" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X14" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>44073</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>165500</v>
+      </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AG14" t="n">
+        <v>4275658</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4318213</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>13904703</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>8593871</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>85160</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>177</v>
+      </c>
+      <c r="E15" t="n">
+        <v>177</v>
+      </c>
+      <c r="F15" t="n">
+        <v>177</v>
+      </c>
+      <c r="G15" t="n">
+        <v>177</v>
+      </c>
+      <c r="H15" t="n">
+        <v>177</v>
+      </c>
+      <c r="I15" t="n">
+        <v>177</v>
+      </c>
+      <c r="J15" t="n">
+        <v>177</v>
+      </c>
+      <c r="K15" t="n">
+        <v>177</v>
+      </c>
+      <c r="L15" t="n">
+        <v>177</v>
+      </c>
+      <c r="M15" t="n">
+        <v>598</v>
+      </c>
+      <c r="N15" t="n">
+        <v>598</v>
+      </c>
+      <c r="O15" t="n">
+        <v>598</v>
+      </c>
+      <c r="P15" t="n">
+        <v>598</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>598</v>
+      </c>
+      <c r="R15" t="n">
+        <v>113</v>
+      </c>
+      <c r="S15" t="n">
+        <v>113</v>
+      </c>
+      <c r="T15" t="n">
+        <v>177</v>
+      </c>
+      <c r="U15" t="n">
+        <v>177</v>
+      </c>
+      <c r="V15" t="n">
+        <v>177</v>
+      </c>
+      <c r="W15" t="n">
+        <v>177</v>
+      </c>
+      <c r="X15" t="n">
+        <v>177</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>177</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>177</v>
+      </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>177</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>177</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>177</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>177</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>598</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>units_short</t>
         </is>
@@ -2461,9 +3145,10 @@
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>title</t>
         </is>
@@ -2475,359 +3160,369 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Australia Population</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A2133244X</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>A2133245A</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>A2133246C</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>A2133247F</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>A2133248J</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>A2133249K</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>A2133251W</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>A2133255F</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>A2133256J</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>A85232567K</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>A85232568L</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>A85232561W</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A85232566J</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>A85232570X</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>A2603609J</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>A2603610T</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>A2060842F</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>A2133252X</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>A2133253A</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>A2133250V</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2133254C</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>A2060784V</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>A2060785W</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>A85232558J,340102</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>A85232568L,340101</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>A2325941A</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>A2326391L</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>A2325946L</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>A2325981V</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GLFSEPTPOP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>australia/population</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>A2133244X</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>A2133245A</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>A2133246C</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>A2133247F</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>A2133248J</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>A2133249K</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>A2133251W</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>A2133255F</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>A2133256J</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>A85232567K</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>A85232568L</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>A85232561W</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>A85232566J</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>A85232570X</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>A2603609J</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>A2603610T</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>A2060842F</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>A2133252X</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>A2133253A</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>A2133250V</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>A2133254C</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>A2060784V</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>A2060785W</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>A85232558J,340102</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>A85232568L,340101</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>A2325941A</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>A2326391L</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>A2325946L</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>A2325981V</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>A2060825C</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>A2060834F</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>A2060833C</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>A2060843J</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GLFSEPTPOP</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>australia/population</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>A2133244X</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>A2133245A</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>A2133246C</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>A2133247F</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>A2133248J</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>A2133249K</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>A2133251W</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>A2133255F</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>A2133256J</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>A85232567K</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>A85232568L</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>A85232561W</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>A85232566J</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>A85232570X</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>A2603609J</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>A2603610T</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>A2060842F</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>A2133252X</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>A2133253A</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>A2133250V</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>A2133254C</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>A2060784V</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>A2060785W</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>A85232558J,340102</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>A85232568L,340101</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>A2325941A</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>A2326391L</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>A2325946L</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>A2325981V</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>A2060825C</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>A2060834F</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>A2060833C</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>A2060843J</t>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
@@ -2867,6 +3562,2764 @@
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>A2133244X</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>A2133245A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>A2133252X</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>A2133246C</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>A2133247F</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>A2133248J</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>A2133249K</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>A2133253A</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>A2133250V</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>A2133254C</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>A2133251W</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>A2133255F</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>A2133256J</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>A85232567K</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>A85232568L</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>A85232561W</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>A2060784V</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>A2060785W</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>A85232566J</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>A85232570X</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>A2603609J</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>A2603610T</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>A2060842F</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>australia/population</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Catalogue number</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>3401.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3401.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3401.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3401.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3401.0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6345.0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>6345.0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3101.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3401.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Collection Month</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Data Item Description</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Births ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Deaths ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Natural Increase ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Interstate Arrivals ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Interstate Departures ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Overseas Arrivals ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Overseas Departures ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Net Permanent and Long Term Movement ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Migration Adjustment ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Net Overseas Migration ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population (ERP) ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ERP Change Over Previous Year ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Percentage ERP Change Over Previous Year ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Number of movements ;  Permanent Arrivals ;</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Number of movements ;  Permanent and Long-term Arrivals ;</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Number of movements ;  Total Arrivals ;</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Natural Increase ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Net Overseas Migration ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Number of movements ;  Permanent Departures ;</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Number of movements ;  Total Departures ;</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Quarterly Index ;  Total hourly rates of pay excluding bonuses ;  Australia ;  Private and Public ;  All industries ;</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Percentage Change from Previous Quarter ;  Total hourly rates of pay excluding bonuses ;  Australia ;  Private and Public ;  All industries ;</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Persons ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Male ;  New South Wales ;</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Female ;  New South Wales ;</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Female ;  Australia ;</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population ;  Persons ;  New South Wales ;</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Number of movements ;  Permanent and Long-term Departures ;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PERCENT</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>INDEX</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>PERCENT</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>STOCK_CLOSE</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Freq.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>No. Obs.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Series End</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2025-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Series ID</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A2133244X</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A2133245A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A2133252X</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A2133246C</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>A2133247F</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A2133248J</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>A2133249K</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>A2133253A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>A2133250V</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>A2133254C</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>A2133251W</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A2133255F</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>A2133256J</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>A85232567K</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A85232568L</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>A85232561W</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>A2060784V</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>A2060785W</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>A85232566J</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>A85232570X</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>A2603609J</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>A2603610T</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A2060842F</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Series Start</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1976-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1976-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1976-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1976-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1976-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1997-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1997-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1981-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1976-01-01 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Series Type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>340101</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>340101</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>340101</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>310102</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>310102</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>340102</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>340102</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>634501</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>634501</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>310104</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>310104</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>310104</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>310104</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>310104</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>340102</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Table Description</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Population Change, Summary - Australia ('000)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Table 1: Total Movement, Arrivals - Category of Movement</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Table 1: Total Movement, Arrivals - Category of Movement</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Table 1: Total Movement, Arrivals - Category of Movement</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Population Change, Components - States and Territories (Number)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Population Change, Components - States and Territories (Number)</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Table 2: Total Movement, Departures - Category of Movement</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Table 2: Total Movement, Departures - Category of Movement</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Total Hourly Rates of Pay Excluding Bonuses: Sector, Original, Seasonally Adjusted and Trend</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Total Hourly Rates of Pay Excluding Bonuses: Sector, Original, Seasonally Adjusted and Trend</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population, States and Territories (Number)</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population, States and Territories (Number)</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population, States and Territories (Number)</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population, States and Territories (Number)</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Estimated Resident Population, States and Territories (Number)</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Table 2: Total Movement, Departures - Category of Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Index Numbers</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Persons</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Persons</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Persons</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Persons</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Persons</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>australia</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>The population of Australia represents 0.33 percent of the world´s total population which arguably means that one person in every 308 people on the planet is a resident of Australia.</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>YS-JAN</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>australia/population</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>indicator</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>max_value</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>27.68</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>min_value</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>24.39</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>original_source</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Australian Bureau of Statistics</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Trading Economics</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A2133244X</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A2133245A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A2133252X</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>A2133246C</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>A2133247F</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>A2133248J</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>A2133249K</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>A2133253A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>A2133250V</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>A2133254C</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>A2133251W</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A2133255F</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>A2133256J</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>A85232567K</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A85232568L</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A85232561W</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>A2060784V</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>A2060785W</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>A85232566J</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>A85232570X</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>A2603609J</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>A2603610T</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2060842F</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>A2060825C</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>A2060834F</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>A2060833C</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>A2060843J</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Australia Population</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>A85232558J</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Million</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
